--- a/gamer_forms/028_virtual_reality_production_grant_application--gamer_forms.xlsx
+++ b/gamer_forms/028_virtual_reality_production_grant_application--gamer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -899,8 +899,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -928,12 +928,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_0,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 0, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'budget_and_timeline'}</t>
+          <t>budget_and_timeline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Budget and timeline'}</t>
+          <t>Budget and timeline</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'project_proposal'}</t>
+          <t>project_proposal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Project proposal'}</t>
+          <t>Project proposal</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'production_plan'}</t>
+          <t>production_plan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Production plan'}</t>
+          <t>Production plan</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'project_deliverables'}</t>
+          <t>project_deliverables</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Project deliverables'}</t>
+          <t>Project deliverables</t>
         </is>
       </c>
     </row>
